--- a/education_forms/045_kids_cooking_class_allergy_form--education_forms.xlsx
+++ b/education_forms/045_kids_cooking_class_allergy_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Contact Relationship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Doctor Phone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Doctor Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>allergic_to_shellfish</t>
+          <t>allergic_to_wheat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allergic to shellfish</t>
+          <t>Allergic to wheat</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>allergic_to_wheat</t>
+          <t>allergic_to_milk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allergic to wheat</t>
+          <t>Allergic to milk</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>allergic_to_milk</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allergic to milk</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allergy_1_type_choices</t>
+          <t>allergy_1_severity_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mild</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>allergy_1_severity_choices</t>
+          <t>allergy_2_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>allergic_to_peanuts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Allergic to peanuts</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>allergic_to_peanuts</t>
+          <t>allergic_to_dairy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allergic to peanuts</t>
+          <t>Allergic to dairy</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>allergic_to_dairy</t>
+          <t>allergic_to_eggs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allergic to dairy</t>
+          <t>Allergic to eggs</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>allergic_to_eggs</t>
+          <t>allergic_to_gluten</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Allergic to eggs</t>
+          <t>Allergic to gluten</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>allergic_to_gluten</t>
+          <t>allergic_to_shellfish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allergic to gluten</t>
+          <t>Allergic to shellfish</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>allergic_to_shellfish</t>
+          <t>allergic_to_soy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allergic to shellfish</t>
+          <t>Allergic to soy</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>allergic_to_soy</t>
+          <t>allergic_to_tree_nuts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allergic to soy</t>
+          <t>Allergic to tree nuts</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>allergic_to_tree_nuts</t>
+          <t>allergic_to_fish</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Allergic to tree nuts</t>
+          <t>Allergic to fish</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>allergic_to_fish</t>
+          <t>allergic_to_wheat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Allergic to fish</t>
+          <t>Allergic to wheat</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>allergic_to_shellfish</t>
+          <t>allergic_to_milk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allergic to shellfish</t>
+          <t>Allergic to milk</t>
         </is>
       </c>
     </row>
@@ -1539,46 +1539,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>allergic_to_wheat</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allergic to wheat</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>allergy_2_type_choices</t>
+          <t>allergy_2_severity_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>allergic_to_milk</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Allergic to milk</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>allergy_2_type_choices</t>
+          <t>allergy_2_severity_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1590,44 +1590,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Severe</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>allergy_2_severity_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>mild</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Mild</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>allergy_2_severity_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
